--- a/BurnDownChart - Maply Services.xlsx
+++ b/BurnDownChart - Maply Services.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>Maply Services</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Burn Down Chart</t>
@@ -214,11 +214,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1524599581"/>
-        <c:axId val="1632653548"/>
+        <c:axId val="935879820"/>
+        <c:axId val="2140703375"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1524599581"/>
+        <c:axId val="935879820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -274,10 +274,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1632653548"/>
+        <c:crossAx val="2140703375"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1632653548"/>
+        <c:axId val="2140703375"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -354,7 +354,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1524599581"/>
+        <c:crossAx val="935879820"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -732,8 +732,8 @@
         <v>46199.0</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="3">
-        <v>0.0</v>
+      <c r="C16" s="5">
+        <v>31.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -741,7 +741,7 @@
         <v>46206.0</v>
       </c>
       <c r="C17" s="7">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">

--- a/BurnDownChart - Maply Services.xlsx
+++ b/BurnDownChart - Maply Services.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="vW/DhlBXCYERPEtfGGte0DmLJeKHvSkRZ4iY0JqySH4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="XmcZaxOAOzN62rMD5gCYvp6rem1Ts/Ft+xhN4+Dwuz4="/>
     </ext>
   </extLst>
 </workbook>
@@ -92,6 +92,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -100,9 +103,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
@@ -214,11 +214,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="935879820"/>
-        <c:axId val="2140703375"/>
+        <c:axId val="1318771449"/>
+        <c:axId val="1303199763"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="935879820"/>
+        <c:axId val="1318771449"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -274,10 +274,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2140703375"/>
+        <c:crossAx val="1303199763"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2140703375"/>
+        <c:axId val="1303199763"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -354,7 +354,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="935879820"/>
+        <c:crossAx val="1318771449"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -384,15 +384,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1630306340" name="Chart 1" title="Gráfico"/>
+        <xdr:cNvPr id="71617620" name="Chart 1" title="Gráfico"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -635,144 +635,145 @@
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>46122.0</v>
       </c>
-      <c r="B5" s="5">
-        <v>73.0</v>
-      </c>
-      <c r="C5" s="5">
-        <v>73.0</v>
+      <c r="B5" s="6">
+        <v>86.0</v>
+      </c>
+      <c r="C5" s="6">
+        <v>86.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>46129.0</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
+        <v>79.0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="5">
+        <v>46136.0</v>
+      </c>
+      <c r="C7" s="6">
         <v>65.0</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4">
-        <v>46136.0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>49.0</v>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <v>46143.0</v>
       </c>
-      <c r="C8" s="3">
-        <v>49.0</v>
+      <c r="C8" s="6">
+        <v>65.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <v>46150.0</v>
       </c>
-      <c r="C9" s="5">
-        <v>49.0</v>
+      <c r="C9" s="6">
+        <v>65.0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <v>46157.0</v>
       </c>
-      <c r="C10" s="5">
-        <v>46.0</v>
+      <c r="C10" s="6">
+        <v>61.0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <v>46164.0</v>
       </c>
-      <c r="C11" s="5">
-        <v>46.0</v>
+      <c r="C11" s="6">
+        <v>61.0</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <v>46171.0</v>
       </c>
-      <c r="C12" s="5">
-        <v>46.0</v>
+      <c r="C12" s="6">
+        <v>61.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>46178.0</v>
       </c>
-      <c r="C13" s="5">
-        <v>44.0</v>
+      <c r="C13" s="6">
+        <v>59.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="6">
+      <c r="A14" s="7">
         <v>46185.0</v>
       </c>
-      <c r="C14" s="5">
-        <v>41.0</v>
+      <c r="C14" s="6">
+        <v>56.0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <v>46192.0</v>
       </c>
-      <c r="C15" s="5">
-        <v>39.0</v>
+      <c r="C15" s="6">
+        <v>51.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4">
+      <c r="A16" s="5">
         <v>46199.0</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="5">
-        <v>31.0</v>
+      <c r="C16" s="6">
+        <v>42.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="4">
+      <c r="A17" s="5">
         <v>46206.0</v>
       </c>
-      <c r="C17" s="7">
-        <v>22.0</v>
+      <c r="C17" s="4">
+        <v>32.0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4">
+      <c r="A18" s="5">
         <v>46213.0</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="4">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="5">
+        <v>46220.0</v>
+      </c>
+      <c r="C19" s="4">
         <v>0.0</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="4">
-        <v>46220.0</v>
-      </c>
-      <c r="C19" s="7">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="C20" s="4">
         <v>0.0</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4">
+      <c r="A21" s="5">
         <v>46234.0</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -780,7 +781,7 @@
       <c r="A22" s="8">
         <v>46241.0</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -788,7 +789,7 @@
       <c r="A23" s="9">
         <v>46248.0</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -796,7 +797,7 @@
       <c r="A24" s="9">
         <v>46255.0</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -804,7 +805,7 @@
       <c r="A25" s="9">
         <v>46262.0</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -812,7 +813,7 @@
       <c r="A26" s="8">
         <v>46269.0</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -820,7 +821,7 @@
       <c r="A27" s="9">
         <v>46276.0</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -828,7 +829,7 @@
       <c r="A28" s="9">
         <v>46283.0</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -836,7 +837,7 @@
       <c r="A29" s="9">
         <v>46290.0</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -844,7 +845,7 @@
       <c r="A30" s="8">
         <v>46297.0</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -852,7 +853,7 @@
       <c r="A31" s="8">
         <v>46304.0</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -860,7 +861,7 @@
       <c r="A32" s="9">
         <v>46311.0</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -868,7 +869,7 @@
       <c r="A33" s="9">
         <v>46318.0</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -876,7 +877,7 @@
       <c r="A34" s="9">
         <v>46325.0</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -884,7 +885,7 @@
       <c r="A35" s="8">
         <v>46332.0</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="4">
         <v>0.0</v>
       </c>
     </row>
@@ -895,7 +896,7 @@
       <c r="B36" s="3">
         <v>0.0</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="4">
         <v>0.0</v>
       </c>
     </row>
